--- a/outputs/tables/tab-11-cursos.xlsx
+++ b/outputs/tables/tab-11-cursos.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E137"/>
+  <dimension ref="A1:E127"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -398,10 +398,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>656</v>
+        <v>450</v>
       </c>
       <c r="E2">
-        <v>0.4542682926829268</v>
+        <v>0.4666666666666667</v>
       </c>
     </row>
     <row r="3">
@@ -421,10 +421,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>1071</v>
+        <v>741</v>
       </c>
       <c r="E3">
-        <v>0.361344537815126</v>
+        <v>0.4048582995951417</v>
       </c>
     </row>
     <row r="4">
@@ -435,42 +435,42 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Faculdade de Ciências Farmacêuticas de Ribeirão Preto</t>
+          <t>Faculdade de Odontologia de Bauru</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Farmácia - Bioquímica</t>
+          <t>Fonoaudiologia</t>
         </is>
       </c>
       <c r="D4">
-        <v>836</v>
+        <v>314</v>
       </c>
       <c r="E4">
-        <v>0.3480861244019139</v>
+        <v>0.4012738853503185</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ciências Agrárias</t>
+          <t>Ciências Sociais Aplicadas</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Faculdade de Zootecnia e Engenharia de Alimentos</t>
+          <t>Instituto de Arquitetura e Urbanismo de São Carlos</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Medicina Veterinária</t>
+          <t>Arquitetura e Urbanismo</t>
         </is>
       </c>
       <c r="D5">
-        <v>838</v>
+        <v>384</v>
       </c>
       <c r="E5">
-        <v>0.3317422434367542</v>
+        <v>0.4010416666666667</v>
       </c>
     </row>
     <row r="6">
@@ -490,79 +490,79 @@
         </is>
       </c>
       <c r="D6">
-        <v>1098</v>
+        <v>767</v>
       </c>
       <c r="E6">
-        <v>0.3306010928961748</v>
+        <v>0.3989569752281616</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ciências Sociais Aplicadas</t>
+          <t>Ciências da Saúde</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Instituto de Arquitetura e Urbanismo de São Carlos</t>
+          <t>Escola de Enfermagem de Ribeirão Preto</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Arquitetura e Urbanismo</t>
+          <t>Bacharelado e Licenciatura em Enfermagem</t>
         </is>
       </c>
       <c r="D7">
-        <v>575</v>
+        <v>447</v>
       </c>
       <c r="E7">
-        <v>0.3286956521739131</v>
+        <v>0.3870246085011186</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ciências da Saúde</t>
+          <t>Multidisciplinar</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Faculdade de Odontologia de Bauru</t>
+          <t>Faculdade de Filosofia, Ciências e Letras de Ribeirão Preto</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Fonoaudiologia</t>
+          <t>Ciências Biológicas</t>
         </is>
       </c>
       <c r="D8">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E8">
-        <v>0.3284518828451883</v>
+        <v>0.3773584905660378</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Multidisciplinar</t>
+          <t>Ciências Agrárias</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Faculdade de Filosofia, Ciências e Letras de Ribeirão Preto</t>
+          <t>Faculdade de Zootecnia e Engenharia de Alimentos</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ciências Biológicas</t>
+          <t>Medicina Veterinária</t>
         </is>
       </c>
       <c r="D9">
-        <v>651</v>
+        <v>580</v>
       </c>
       <c r="E9">
-        <v>0.3271889400921659</v>
+        <v>0.3586206896551724</v>
       </c>
     </row>
     <row r="10">
@@ -573,19 +573,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Faculdade de Medicina</t>
+          <t>Faculdade de Ciências Farmacêuticas de Ribeirão Preto</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Fonoaudiologia</t>
+          <t>Farmácia - Bioquímica</t>
         </is>
       </c>
       <c r="D10">
-        <v>344</v>
+        <v>754</v>
       </c>
       <c r="E10">
-        <v>0.313953488372093</v>
+        <v>0.3488063660477453</v>
       </c>
     </row>
     <row r="11">
@@ -596,19 +596,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Escola de Enfermagem de Ribeirão Preto</t>
+          <t>Faculdade de Odontologia de Ribeirão Preto</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bacharelado e Licenciatura em Enfermagem</t>
+          <t>Odontologia</t>
         </is>
       </c>
       <c r="D11">
-        <v>672</v>
+        <v>730</v>
       </c>
       <c r="E11">
-        <v>0.3095238095238095</v>
+        <v>0.3479452054794521</v>
       </c>
     </row>
     <row r="12">
@@ -619,19 +619,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Faculdade de Medicina de Ribeirão Preto</t>
+          <t>Faculdade de Medicina</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ciências Médicas - Ciclo Básico</t>
+          <t>Fisioterapia</t>
         </is>
       </c>
       <c r="D12">
-        <v>503</v>
+        <v>243</v>
       </c>
       <c r="E12">
-        <v>0.2982107355864811</v>
+        <v>0.3415637860082305</v>
       </c>
     </row>
     <row r="13">
@@ -642,7 +642,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Faculdade de Odontologia de Ribeirão Preto</t>
+          <t>Faculdade de Odontologia</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -651,10 +651,10 @@
         </is>
       </c>
       <c r="D13">
-        <v>1051</v>
+        <v>1214</v>
       </c>
       <c r="E13">
-        <v>0.2892483349191247</v>
+        <v>0.329489291598023</v>
       </c>
     </row>
     <row r="14">
@@ -665,19 +665,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Escola de Enfermagem de Ribeirão Preto</t>
+          <t>Faculdade de Medicina</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Enfermagem</t>
+          <t>Fonoaudiologia</t>
         </is>
       </c>
       <c r="D14">
-        <v>1092</v>
+        <v>235</v>
       </c>
       <c r="E14">
-        <v>0.2875457875457875</v>
+        <v>0.3276595744680851</v>
       </c>
     </row>
     <row r="15">
@@ -688,65 +688,65 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Faculdade de Medicina</t>
+          <t>Escola de Enfermagem de Ribeirão Preto</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Fisioterapia</t>
+          <t>Enfermagem</t>
         </is>
       </c>
       <c r="D15">
-        <v>350</v>
+        <v>737</v>
       </c>
       <c r="E15">
-        <v>0.2857142857142857</v>
+        <v>0.3242876526458616</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ciências Biológicas</t>
+          <t>Ciências da Saúde</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Instituto de Ciências Biomédicas</t>
+          <t>Faculdade de Medicina de Ribeirão Preto</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bacharelado em Ciências Biomédicas</t>
+          <t>Fisioterapia</t>
         </is>
       </c>
       <c r="D16">
-        <v>468</v>
+        <v>368</v>
       </c>
       <c r="E16">
-        <v>0.2777777777777778</v>
+        <v>0.3206521739130435</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ciências da Saúde</t>
+          <t>Ciências Agrárias</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Faculdade de Odontologia</t>
+          <t>Escola Superior de Agricultura "Luiz de Queiroz"</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Odontologia</t>
+          <t>Ciências Biológicas</t>
         </is>
       </c>
       <c r="D17">
-        <v>1766</v>
+        <v>278</v>
       </c>
       <c r="E17">
-        <v>0.2729331823329558</v>
+        <v>0.3201438848920863</v>
       </c>
     </row>
     <row r="18">
@@ -762,37 +762,37 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Fisioterapia</t>
+          <t>Ciências Médicas - Ciclo Básico</t>
         </is>
       </c>
       <c r="D18">
-        <v>531</v>
+        <v>503</v>
       </c>
       <c r="E18">
-        <v>0.2693032015065913</v>
+        <v>0.2982107355864811</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ciências Agrárias</t>
+          <t>Multidisciplinar</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Escola Superior de Agricultura "Luiz de Queiroz"</t>
+          <t>Faculdade de Filosofia, Ciências e Letras de Ribeirão Preto</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ciências Biológicas</t>
+          <t>Psicologia</t>
         </is>
       </c>
       <c r="D19">
-        <v>402</v>
+        <v>384</v>
       </c>
       <c r="E19">
-        <v>0.2686567164179104</v>
+        <v>0.296875</v>
       </c>
     </row>
     <row r="20">
@@ -812,21 +812,21 @@
         </is>
       </c>
       <c r="D20">
-        <v>545</v>
+        <v>377</v>
       </c>
       <c r="E20">
-        <v>0.255045871559633</v>
+        <v>0.2891246684350133</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Multidisciplinar</t>
+          <t>Ciências Humanas</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Faculdade de Filosofia, Ciências e Letras de Ribeirão Preto</t>
+          <t>Instituto de Psicologia</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="D21">
-        <v>546</v>
+        <v>683</v>
       </c>
       <c r="E21">
-        <v>0.2527472527472527</v>
+        <v>0.2869692532942899</v>
       </c>
     </row>
     <row r="22">
@@ -858,79 +858,79 @@
         </is>
       </c>
       <c r="D22">
-        <v>397</v>
+        <v>276</v>
       </c>
       <c r="E22">
-        <v>0.2518891687657431</v>
+        <v>0.286231884057971</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ciências Exatas e da Terra</t>
+          <t>Ciências Biológicas</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Instituto de Astronomia, Geofísica e Ciências Atmosféricas</t>
+          <t>Instituto de Ciências Biomédicas</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bacharelado em Astronomia</t>
+          <t>Bacharelado em Ciências Biomédicas</t>
         </is>
       </c>
       <c r="D23">
-        <v>280</v>
+        <v>293</v>
       </c>
       <c r="E23">
-        <v>0.2428571428571429</v>
+        <v>0.2832764505119454</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Ciências Humanas</t>
+          <t>Ciências Agrárias</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Instituto de Psicologia</t>
+          <t>Faculdade de Zootecnia e Engenharia de Alimentos</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Psicologia</t>
+          <t>Engenharia de Alimentos</t>
         </is>
       </c>
       <c r="D24">
-        <v>977</v>
+        <v>958</v>
       </c>
       <c r="E24">
-        <v>0.2425793244626407</v>
+        <v>0.2703549060542798</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ciências da Saúde</t>
+          <t>Ciências Agrárias</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Faculdade de Medicina de Ribeirão Preto</t>
+          <t>Escola Superior de Agricultura "Luiz de Queiroz"</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ciências Biomédicas</t>
+          <t>Ciências dos Alimentos</t>
         </is>
       </c>
       <c r="D25">
-        <v>228</v>
+        <v>370</v>
       </c>
       <c r="E25">
-        <v>0.2368421052631579</v>
+        <v>0.2513513513513513</v>
       </c>
     </row>
     <row r="26">
@@ -950,102 +950,102 @@
         </is>
       </c>
       <c r="D26">
-        <v>2065</v>
+        <v>1423</v>
       </c>
       <c r="E26">
-        <v>0.223728813559322</v>
+        <v>0.2459592410400562</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Ciências Agrárias</t>
+          <t>Ciências da Saúde</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Faculdade de Zootecnia e Engenharia de Alimentos</t>
+          <t>Faculdade de Medicina de Ribeirão Preto</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Engenharia de Alimentos</t>
+          <t>Medicina</t>
         </is>
       </c>
       <c r="D27">
-        <v>1387</v>
+        <v>400</v>
       </c>
       <c r="E27">
-        <v>0.2235039653929344</v>
+        <v>0.2425</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Ciências da Saúde</t>
+          <t>Ciências Agrárias</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Faculdade de Ciências Farmacêuticas</t>
+          <t>Faculdade de Zootecnia e Engenharia de Alimentos</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Farmácia - Bioquímica</t>
+          <t>Engenharia de Biossistemas</t>
         </is>
       </c>
       <c r="D28">
-        <v>1520</v>
+        <v>531</v>
       </c>
       <c r="E28">
-        <v>0.2217105263157895</v>
+        <v>0.2354048964218456</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Ciências Agrárias</t>
+          <t>Engenharias</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Escola Superior de Agricultura "Luiz de Queiroz"</t>
+          <t>Escola de Engenharia de São Carlos</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ciências dos Alimentos</t>
+          <t>Engenharia Civil</t>
         </is>
       </c>
       <c r="D29">
-        <v>527</v>
+        <v>551</v>
       </c>
       <c r="E29">
-        <v>0.2182163187855788</v>
+        <v>0.2323049001814882</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Ciências da Saúde</t>
+          <t>Engenharias</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Faculdade de Medicina</t>
+          <t>Escola de Engenharia de São Carlos</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Medicina</t>
+          <t>Engenharia Ambiental</t>
         </is>
       </c>
       <c r="D30">
-        <v>2287</v>
+        <v>391</v>
       </c>
       <c r="E30">
-        <v>0.2116309575863577</v>
+        <v>0.2301790281329923</v>
       </c>
     </row>
     <row r="31">
@@ -1065,194 +1065,194 @@
         </is>
       </c>
       <c r="D31">
-        <v>809</v>
+        <v>558</v>
       </c>
       <c r="E31">
-        <v>0.211372064276885</v>
+        <v>0.2293906810035842</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Engenharias</t>
+          <t>Ciências da Saúde</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Escola de Engenharia de São Carlos</t>
+          <t>Faculdade de Medicina</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Engenharia Ambiental</t>
+          <t>Medicina</t>
         </is>
       </c>
       <c r="D32">
-        <v>560</v>
+        <v>1585</v>
       </c>
       <c r="E32">
-        <v>0.2035714285714286</v>
+        <v>0.2227129337539432</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Engenharias</t>
+          <t>Ciências da Saúde</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Escola de Engenharia de Lorena</t>
+          <t>Faculdade de Saúde Pública</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Engenharia Bioquímica</t>
+          <t>Nutrição</t>
         </is>
       </c>
       <c r="D33">
-        <v>528</v>
+        <v>767</v>
       </c>
       <c r="E33">
-        <v>0.2007575757575757</v>
+        <v>0.2177314211212516</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Ciências Agrárias</t>
+          <t>Ciências da Saúde</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Faculdade de Zootecnia e Engenharia de Alimentos</t>
+          <t>Faculdade de Ciências Farmacêuticas</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Engenharia de Biossistemas</t>
+          <t>Farmácia - Bioquímica</t>
         </is>
       </c>
       <c r="D34">
-        <v>756</v>
+        <v>1367</v>
       </c>
       <c r="E34">
-        <v>0.1984126984126984</v>
+        <v>0.2172640819312363</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Ciências da Saúde</t>
+          <t>Ciências Agrárias</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Faculdade de Saúde Pública</t>
+          <t>Faculdade de Zootecnia e Engenharia de Alimentos</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Nutrição</t>
+          <t>Zootecnia</t>
         </is>
       </c>
       <c r="D35">
-        <v>1112</v>
+        <v>407</v>
       </c>
       <c r="E35">
-        <v>0.1951438848920863</v>
+        <v>0.2137592137592138</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Ciências Agrárias</t>
+          <t>Ciências Biológicas</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Faculdade de Zootecnia e Engenharia de Alimentos</t>
+          <t>Instituto de Biociências</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Zootecnia</t>
+          <t>Ciências Biológicas</t>
         </is>
       </c>
       <c r="D36">
-        <v>593</v>
+        <v>1136</v>
       </c>
       <c r="E36">
-        <v>0.193929173693086</v>
+        <v>0.2015845070422535</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Ciências da Saúde</t>
+          <t>Ciências Exatas e da Terra</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Faculdade de Odontologia de Bauru</t>
+          <t>Instituto de Química</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Medicina</t>
+          <t>Química</t>
         </is>
       </c>
       <c r="D37">
-        <v>305</v>
+        <v>915</v>
       </c>
       <c r="E37">
-        <v>0.1901639344262295</v>
+        <v>0.1989071038251366</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Engenharias</t>
+          <t>Ciências Exatas e da Terra</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Escola de Engenharia de São Carlos</t>
+          <t>Instituto de Física de São Carlos</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Engenharia Civil</t>
+          <t>Física</t>
         </is>
       </c>
       <c r="D38">
-        <v>801</v>
+        <v>451</v>
       </c>
       <c r="E38">
-        <v>0.1872659176029963</v>
+        <v>0.1951219512195122</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Ciências Biológicas</t>
+          <t>Engenharias</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Instituto de Biociências</t>
+          <t>Escola de Engenharia de Lorena</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ciências Biológicas</t>
+          <t>Engenharia Bioquímica</t>
         </is>
       </c>
       <c r="D39">
-        <v>1654</v>
+        <v>370</v>
       </c>
       <c r="E39">
-        <v>0.1777509068923821</v>
+        <v>0.1945945945945946</v>
       </c>
     </row>
     <row r="40">
@@ -1272,217 +1272,217 @@
         </is>
       </c>
       <c r="D40">
-        <v>833</v>
+        <v>574</v>
       </c>
       <c r="E40">
-        <v>0.177671068427371</v>
+        <v>0.1881533101045296</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Ciências Exatas e da Terra</t>
+          <t>Ciências da Saúde</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Instituto de Física de São Carlos</t>
+          <t>Faculdade de Saúde Pública</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Física</t>
+          <t>Bacharelado em Saúde Pública</t>
         </is>
       </c>
       <c r="D41">
-        <v>632</v>
+        <v>284</v>
       </c>
       <c r="E41">
-        <v>0.1772151898734177</v>
+        <v>0.1866197183098592</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Multidisciplinar</t>
+          <t>Ciências Exatas e da Terra</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Faculdade de Filosofia, Ciências e Letras de Ribeirão Preto</t>
+          <t>Instituto de Geociências</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bacharelado em Física Médica</t>
+          <t>Geologia</t>
         </is>
       </c>
       <c r="D42">
-        <v>592</v>
+        <v>499</v>
       </c>
       <c r="E42">
-        <v>0.1722972972972973</v>
+        <v>0.1843687374749499</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Ciências da Saúde</t>
+          <t>Engenharias</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Faculdade de Ciências Farmacêuticas de Ribeirão Preto</t>
+          <t>Escola de Engenharia de São Carlos</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Farmácia</t>
+          <t>Engenharia de Materiais e Manufatura</t>
         </is>
       </c>
       <c r="D43">
-        <v>256</v>
+        <v>488</v>
       </c>
       <c r="E43">
-        <v>0.1640625</v>
+        <v>0.1823770491803279</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Ciências Exatas e da Terra</t>
+          <t>Engenharias</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Instituto de Geociências</t>
+          <t>Escola de Engenharia de São Carlos</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Geologia</t>
+          <t>Engenharia Mecânica</t>
         </is>
       </c>
       <c r="D44">
-        <v>723</v>
+        <v>452</v>
       </c>
       <c r="E44">
-        <v>0.1618257261410788</v>
+        <v>0.1814159292035398</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Engenharias</t>
+          <t>Multidisciplinar</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Escola de Engenharia de São Carlos</t>
+          <t>Faculdade de Filosofia, Ciências e Letras de Ribeirão Preto</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Engenharia de Materiais e Manufatura</t>
+          <t>Bacharelado em Física Médica</t>
         </is>
       </c>
       <c r="D45">
-        <v>696</v>
+        <v>408</v>
       </c>
       <c r="E45">
-        <v>0.1594827586206897</v>
+        <v>0.1813725490196078</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Ciências da Saúde</t>
+          <t>Multidisciplinar</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Faculdade de Saúde Pública</t>
+          <t>Pró-reitoria de Graduação</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bacharelado em Saúde Pública</t>
+          <t>Ciências Moleculares</t>
         </is>
       </c>
       <c r="D46">
-        <v>453</v>
+        <v>227</v>
       </c>
       <c r="E46">
-        <v>0.1589403973509934</v>
+        <v>0.1806167400881057</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Ciências da Saúde</t>
+          <t>Linguística, Letras e Artes</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Faculdade de Medicina de Ribeirão Preto</t>
+          <t>Escola de Comunicações e Artes</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Medicina</t>
+          <t>Artes Visuais</t>
         </is>
       </c>
       <c r="D47">
-        <v>800</v>
+        <v>250</v>
       </c>
       <c r="E47">
-        <v>0.15625</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Ciências Agrárias</t>
+          <t>Ciências Exatas e da Terra</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Escola Superior de Agricultura "Luiz de Queiroz"</t>
+          <t>Instituto de Astronomia, Geofísica e Ciências Atmosféricas</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Engenharia Florestal</t>
+          <t>Bacharelado em Geofísica</t>
         </is>
       </c>
       <c r="D48">
-        <v>541</v>
+        <v>337</v>
       </c>
       <c r="E48">
-        <v>0.155268022181146</v>
+        <v>0.1780415430267062</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Ciências Exatas e da Terra</t>
+          <t>Engenharias</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Instituto de Química</t>
+          <t>Escola de Engenharia de São Carlos</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Química</t>
+          <t>Engenharia Mecatrônica</t>
         </is>
       </c>
       <c r="D49">
-        <v>1456</v>
+        <v>472</v>
       </c>
       <c r="E49">
-        <v>0.154532967032967</v>
+        <v>0.1779661016949153</v>
       </c>
     </row>
     <row r="50">
@@ -1502,56 +1502,56 @@
         </is>
       </c>
       <c r="D50">
-        <v>2717</v>
+        <v>1876</v>
       </c>
       <c r="E50">
-        <v>0.1512697828487302</v>
+        <v>0.1753731343283582</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Linguística, Letras e Artes</t>
+          <t>Ciências Agrárias</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Escola de Comunicações e Artes</t>
+          <t>Escola Superior de Agricultura "Luiz de Queiroz"</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Artes Visuais</t>
+          <t>Engenharia Florestal</t>
         </is>
       </c>
       <c r="D51">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="E51">
-        <v>0.1497326203208556</v>
+        <v>0.1684782608695652</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Multidisciplinar</t>
+          <t>Ciências Exatas e da Terra</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Pró-reitoria de Graduação</t>
+          <t>Instituto de Astronomia, Geofísica e Ciências Atmosféricas</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Ciências Moleculares</t>
+          <t>Bacharelado em Meteorologia</t>
         </is>
       </c>
       <c r="D52">
-        <v>355</v>
+        <v>294</v>
       </c>
       <c r="E52">
-        <v>0.1464788732394366</v>
+        <v>0.163265306122449</v>
       </c>
     </row>
     <row r="53">
@@ -1562,88 +1562,88 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Faculdade de Ciências Farmacêuticas</t>
+          <t>Faculdade de Medicina</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Farmácia</t>
+          <t>Terapia Ocupacional</t>
         </is>
       </c>
       <c r="D53">
-        <v>454</v>
+        <v>236</v>
       </c>
       <c r="E53">
-        <v>0.145374449339207</v>
+        <v>0.1610169491525424</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Ciências Exatas e da Terra</t>
+          <t>Ciências Sociais Aplicadas</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Instituto de Física de São Carlos</t>
+          <t>Faculdade de Economia, Administração e Contabilidade de Ribeirão Preto</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bacharelado em Ciências Físicas e Biomoleculares</t>
+          <t>Economia Empresarial e Controladoria</t>
         </is>
       </c>
       <c r="D54">
-        <v>538</v>
+        <v>671</v>
       </c>
       <c r="E54">
-        <v>0.1449814126394052</v>
+        <v>0.1609538002980626</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Multidisciplinar</t>
+          <t>Ciências Exatas e da Terra</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Faculdade de Filosofia, Ciências e Letras de Ribeirão Preto</t>
+          <t>Instituto de Física de São Carlos</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Licenciatura em Química</t>
+          <t>Bacharelado em Ciências Físicas e Biomoleculares</t>
         </is>
       </c>
       <c r="D55">
-        <v>490</v>
+        <v>372</v>
       </c>
       <c r="E55">
-        <v>0.1448979591836735</v>
+        <v>0.1586021505376344</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Engenharias</t>
+          <t>Multidisciplinar</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Escola de Engenharia de São Carlos</t>
+          <t>Faculdade de Filosofia, Ciências e Letras de Ribeirão Preto</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Engenharia Mecânica</t>
+          <t>Licenciatura em Química</t>
         </is>
       </c>
       <c r="D56">
-        <v>658</v>
+        <v>396</v>
       </c>
       <c r="E56">
-        <v>0.1428571428571428</v>
+        <v>0.148989898989899</v>
       </c>
     </row>
     <row r="57">
@@ -1663,125 +1663,125 @@
         </is>
       </c>
       <c r="D57">
-        <v>2432</v>
+        <v>1708</v>
       </c>
       <c r="E57">
-        <v>0.140625</v>
+        <v>0.1446135831381733</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Multidisciplinar</t>
+          <t>Engenharias</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Escola de Artes, Ciências e Humanidades</t>
+          <t>Escola Politécnica</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Bacharelado em Biotecnologia</t>
+          <t>Engenharia</t>
         </is>
       </c>
       <c r="D58">
-        <v>306</v>
+        <v>7932</v>
       </c>
       <c r="E58">
-        <v>0.1405228758169935</v>
+        <v>0.1429652042360061</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Ciências Sociais Aplicadas</t>
+          <t>Ciências da Saúde</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Faculdade de Economia, Administração e Contabilidade de Ribeirão Preto</t>
+          <t>Escola de Educação Física e Esporte de Ribeirão Preto</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Economia Empresarial e Controladoria</t>
+          <t>Educação Física e Esporte</t>
         </is>
       </c>
       <c r="D59">
-        <v>895</v>
+        <v>581</v>
       </c>
       <c r="E59">
-        <v>0.1396648044692737</v>
+        <v>0.1411359724612737</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Ciências Exatas e da Terra</t>
+          <t>Multidisciplinar</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Instituto de Astronomia, Geofísica e Ciências Atmosféricas</t>
+          <t>Escola de Artes, Ciências e Humanidades</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Bacharelado em Geofísica</t>
+          <t>Obstetrícia</t>
         </is>
       </c>
       <c r="D60">
-        <v>467</v>
+        <v>553</v>
       </c>
       <c r="E60">
-        <v>0.139186295503212</v>
+        <v>0.1410488245931284</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Ciências Exatas e da Terra</t>
+          <t>Ciências da Saúde</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Instituto de Astronomia, Geofísica e Ciências Atmosféricas</t>
+          <t>Faculdade de Medicina de Ribeirão Preto</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bacharelado em Meteorologia</t>
+          <t>Fonoaudiologia</t>
         </is>
       </c>
       <c r="D61">
-        <v>418</v>
+        <v>272</v>
       </c>
       <c r="E61">
-        <v>0.138755980861244</v>
+        <v>0.1397058823529412</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Ciências da Saúde</t>
+          <t>Engenharias</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Faculdade de Medicina</t>
+          <t>Escola de Engenharia de Lorena</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Terapia Ocupacional</t>
+          <t>Engenharia de Materiais</t>
         </is>
       </c>
       <c r="D62">
-        <v>346</v>
+        <v>371</v>
       </c>
       <c r="E62">
-        <v>0.138728323699422</v>
+        <v>0.137466307277628</v>
       </c>
     </row>
     <row r="63">
@@ -1797,175 +1797,175 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Engenharia Mecatrônica</t>
+          <t>Engenharia Aeronáutica</t>
         </is>
       </c>
       <c r="D63">
-        <v>671</v>
+        <v>372</v>
       </c>
       <c r="E63">
-        <v>0.1385991058122206</v>
+        <v>0.1370967741935484</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Ciências Sociais Aplicadas</t>
+          <t>Ciências Humanas</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Instituto de Relações Internacionais</t>
+          <t>Faculdade de Filosofia, Letras e Ciências Humanas</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bacharelado em Relações Internacionais</t>
+          <t>Geografia</t>
         </is>
       </c>
       <c r="D64">
-        <v>846</v>
+        <v>1620</v>
       </c>
       <c r="E64">
-        <v>0.1382978723404255</v>
+        <v>0.1358024691358025</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Multidisciplinar</t>
+          <t>Ciências Humanas</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Faculdade de Filosofia, Ciências e Letras de Ribeirão Preto e Faculdade de Medicina de Ribeirão Preto</t>
+          <t>Faculdade de Filosofia, Letras e Ciências Humanas</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Informática Biomédica</t>
+          <t>História</t>
         </is>
       </c>
       <c r="D65">
-        <v>369</v>
+        <v>2524</v>
       </c>
       <c r="E65">
-        <v>0.1327913279132791</v>
+        <v>0.1354992076069731</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Ciências da Saúde</t>
+          <t>Ciências Sociais Aplicadas</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Faculdade de Medicina de Ribeirão Preto</t>
+          <t>Instituto de Relações Internacionais</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Terapia Ocupacional</t>
+          <t>Bacharelado em Relações Internacionais</t>
         </is>
       </c>
       <c r="D66">
-        <v>274</v>
+        <v>589</v>
       </c>
       <c r="E66">
-        <v>0.1313868613138686</v>
+        <v>0.134125636672326</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Engenharias</t>
+          <t>Multidisciplinar</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Escola Politécnica</t>
+          <t>Faculdade de Filosofia, Ciências e Letras de Ribeirão Preto e Faculdade de Medicina de Ribeirão Preto</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Engenharia</t>
+          <t>Informática Biomédica</t>
         </is>
       </c>
       <c r="D67">
-        <v>11518</v>
+        <v>369</v>
       </c>
       <c r="E67">
-        <v>0.1309255079006772</v>
+        <v>0.1327913279132791</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Ciências Humanas</t>
+          <t>Multidisciplinar</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Faculdade de Filosofia, Letras e Ciências Humanas</t>
+          <t>Escola de Engenharia de São Carlos e Instituto de Ciências Matemáticas e de Computação</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>História</t>
+          <t>Engenharia de Computação</t>
         </is>
       </c>
       <c r="D68">
-        <v>3603</v>
+        <v>557</v>
       </c>
       <c r="E68">
-        <v>0.1268387454898696</v>
+        <v>0.1310592459605027</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Ciências Sociais Aplicadas</t>
+          <t>Engenharias</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Faculdade de Arquitetura e Urbanismo</t>
+          <t>Escola de Engenharia de Lorena</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Engenharia Química</t>
         </is>
       </c>
       <c r="D69">
-        <v>559</v>
+        <v>1272</v>
       </c>
       <c r="E69">
-        <v>0.1234347048300537</v>
+        <v>0.1289308176100629</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Engenharias</t>
+          <t>Ciências Humanas</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Escola de Engenharia de Lorena</t>
+          <t>Faculdade de Filosofia, Letras e Ciências Humanas</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Engenharia Química</t>
+          <t>Ciências Sociais</t>
         </is>
       </c>
       <c r="D70">
-        <v>1919</v>
+        <v>2025</v>
       </c>
       <c r="E70">
-        <v>0.1219385096404377</v>
+        <v>0.1264197530864198</v>
       </c>
     </row>
     <row r="71">
@@ -1976,7 +1976,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Escola de Educação Física e Esporte de Ribeirão Preto</t>
+          <t>Escola de Educação Física e Esporte</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -1985,102 +1985,102 @@
         </is>
       </c>
       <c r="D71">
-        <v>772</v>
+        <v>861</v>
       </c>
       <c r="E71">
-        <v>0.1217616580310881</v>
+        <v>0.1254355400696864</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Multidisciplinar</t>
+          <t>Engenharias</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Escola de Engenharia de São Carlos e Instituto de Ciências Matemáticas e de Computação</t>
+          <t>Escola de Engenharia de Lorena</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Engenharia de Computação</t>
+          <t>Engenharia Física</t>
         </is>
       </c>
       <c r="D72">
-        <v>768</v>
+        <v>274</v>
       </c>
       <c r="E72">
-        <v>0.12109375</v>
+        <v>0.1240875912408759</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Ciências Humanas</t>
+          <t>Ciências Sociais Aplicadas</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Faculdade de Filosofia, Letras e Ciências Humanas</t>
+          <t>Faculdade de Economia, Administração e Contabilidade de Ribeirão Preto</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Ciências Sociais</t>
+          <t>Bacharelado em Ciências Econômicas</t>
         </is>
       </c>
       <c r="D73">
-        <v>2905</v>
+        <v>424</v>
       </c>
       <c r="E73">
-        <v>0.1160068846815835</v>
+        <v>0.1155660377358491</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Ciências Humanas</t>
+          <t>Ciências Exatas e da Terra</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Faculdade de Filosofia, Letras e Ciências Humanas</t>
+          <t>Instituto de Ciências Matemáticas e de Computação</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Geografia</t>
+          <t>Bacharelado em Ciências de Computação</t>
         </is>
       </c>
       <c r="D74">
-        <v>2311</v>
+        <v>1099</v>
       </c>
       <c r="E74">
-        <v>0.1151016875811337</v>
+        <v>0.1146496815286624</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Engenharias</t>
+          <t>Ciências Sociais Aplicadas</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Escola de Engenharia de Lorena</t>
+          <t>Faculdade de Direito de Ribeirão Preto</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Engenharia de Materiais</t>
+          <t>Direito</t>
         </is>
       </c>
       <c r="D75">
-        <v>520</v>
+        <v>981</v>
       </c>
       <c r="E75">
-        <v>0.1134615384615385</v>
+        <v>0.1100917431192661</v>
       </c>
     </row>
     <row r="76">
@@ -2091,65 +2091,65 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Escola de Engenharia de Lorena</t>
+          <t>Escola de Engenharia de São Carlos</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Engenharia Física</t>
+          <t>Engenharia Elétrica</t>
         </is>
       </c>
       <c r="D76">
-        <v>429</v>
+        <v>997</v>
       </c>
       <c r="E76">
-        <v>0.1118881118881119</v>
+        <v>0.1073219658976931</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Ciências da Saúde</t>
+          <t>Multidisciplinar</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Faculdade de Medicina de Ribeirão Preto</t>
+          <t>Faculdade de Filosofia, Ciências e Letras de Ribeirão Preto</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Fonoaudiologia</t>
+          <t>Música</t>
         </is>
       </c>
       <c r="D77">
-        <v>391</v>
+        <v>230</v>
       </c>
       <c r="E77">
-        <v>0.1099744245524297</v>
+        <v>0.1043478260869565</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Engenharias</t>
+          <t>Ciências Humanas</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Escola de Engenharia de São Carlos</t>
+          <t>Faculdade de Filosofia, Letras e Ciências Humanas</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Engenharia Aeronáutica</t>
+          <t>Letras</t>
         </is>
       </c>
       <c r="D78">
-        <v>537</v>
+        <v>7661</v>
       </c>
       <c r="E78">
-        <v>0.1098696461824953</v>
+        <v>0.1025975721185224</v>
       </c>
     </row>
     <row r="79">
@@ -2165,152 +2165,152 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Obstetrícia</t>
+          <t>Gerontologia</t>
         </is>
       </c>
       <c r="D79">
-        <v>795</v>
+        <v>501</v>
       </c>
       <c r="E79">
-        <v>0.1094339622641509</v>
+        <v>0.09980039920159681</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Ciências Exatas e da Terra</t>
+          <t>Ciências Sociais Aplicadas</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Instituto de Ciências Matemáticas e de Computação</t>
+          <t>Faculdade de Arquitetura e Urbanismo</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Bacharelado em Ciências de Computação</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="D80">
-        <v>1521</v>
+        <v>380</v>
       </c>
       <c r="E80">
-        <v>0.1051939513477975</v>
+        <v>0.09736842105263158</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Ciências da Saúde</t>
+          <t>Ciências Exatas e da Terra</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Escola de Educação Física e Esporte</t>
+          <t>Instituto de Ciências Matemáticas e de Computação</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Educação Física e Esporte</t>
+          <t>Matemática</t>
         </is>
       </c>
       <c r="D81">
-        <v>1293</v>
+        <v>322</v>
       </c>
       <c r="E81">
-        <v>0.1044083526682135</v>
+        <v>0.09627329192546584</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Engenharias</t>
+          <t>Ciências Humanas</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Escola de Engenharia de São Carlos</t>
+          <t>Faculdade de Filosofia, Letras e Ciências Humanas</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Engenharia Elétrica</t>
+          <t>Filosofia</t>
         </is>
       </c>
       <c r="D82">
-        <v>1400</v>
+        <v>1630</v>
       </c>
       <c r="E82">
-        <v>0.1021428571428571</v>
+        <v>0.08957055214723926</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Ciências Sociais Aplicadas</t>
+          <t>Ciências Agrárias</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Faculdade de Direito de Ribeirão Preto</t>
+          <t>Escola Superior de Agricultura "Luiz de Queiroz"</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Direito</t>
+          <t>Gestão Ambiental</t>
         </is>
       </c>
       <c r="D83">
-        <v>1431</v>
+        <v>371</v>
       </c>
       <c r="E83">
-        <v>0.09923130677847659</v>
+        <v>0.08894878706199461</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Ciências Exatas e da Terra</t>
+          <t>Ciências Sociais Aplicadas</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Instituto de Ciências Matemáticas e de Computação</t>
+          <t>Faculdade de Economia, Administração e Contabilidade de Ribeirão Preto</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Matemática</t>
+          <t>Ciências Contábeis</t>
         </is>
       </c>
       <c r="D84">
-        <v>467</v>
+        <v>426</v>
       </c>
       <c r="E84">
-        <v>0.09635974304068523</v>
+        <v>0.08685446009389672</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Ciências Exatas e da Terra</t>
+          <t>Multidisciplinar</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Instituto de Ciências Matemáticas e de Computação</t>
+          <t>Faculdade de Filosofia, Ciências e Letras de Ribeirão Preto</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Bacharelado em Matemática Aplicada e Computação Científica</t>
+          <t>Bacharelado em Biblioteconomia e Ciência da Informação</t>
         </is>
       </c>
       <c r="D85">
-        <v>383</v>
+        <v>362</v>
       </c>
       <c r="E85">
-        <v>0.09399477806788512</v>
+        <v>0.0856353591160221</v>
       </c>
     </row>
     <row r="86">
@@ -2326,451 +2326,451 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Curso Superior do Audiovisual</t>
+          <t>Música</t>
         </is>
       </c>
       <c r="D86">
-        <v>471</v>
+        <v>269</v>
       </c>
       <c r="E86">
-        <v>0.09129511677282377</v>
+        <v>0.08550185873605948</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Ciências Humanas</t>
+          <t>Linguística, Letras e Artes</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Faculdade de Filosofia, Letras e Ciências Humanas</t>
+          <t>Escola de Comunicações e Artes</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Filosofia</t>
+          <t>Curso Superior do Audiovisual</t>
         </is>
       </c>
       <c r="D87">
-        <v>2342</v>
+        <v>328</v>
       </c>
       <c r="E87">
-        <v>0.08923996584116139</v>
+        <v>0.08231707317073171</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Ciências Sociais Aplicadas</t>
+          <t>Ciências Humanas</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Faculdade de Economia, Administração e Contabilidade de Ribeirão Preto</t>
+          <t>Faculdade de Educação</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Bacharelado em Ciências Econômicas</t>
+          <t>Pedagogia</t>
         </is>
       </c>
       <c r="D88">
-        <v>609</v>
+        <v>1811</v>
       </c>
       <c r="E88">
-        <v>0.08702791461412152</v>
+        <v>0.08227498619547212</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Ciências Humanas</t>
+          <t>Engenharias</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Faculdade de Filosofia, Letras e Ciências Humanas</t>
+          <t>Escola de Engenharia de São Carlos</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Letras</t>
+          <t>Engenharia de Produção</t>
         </is>
       </c>
       <c r="D89">
-        <v>11059</v>
+        <v>252</v>
       </c>
       <c r="E89">
-        <v>0.08689754950718871</v>
+        <v>0.07936507936507936</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Linguística, Letras e Artes</t>
+          <t>Ciências Sociais Aplicadas</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Escola de Comunicações e Artes</t>
+          <t>Faculdade de Economia, Administração e Contabilidade de Ribeirão Preto</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Música</t>
+          <t>Bacharelado em Administração</t>
         </is>
       </c>
       <c r="D90">
-        <v>269</v>
+        <v>966</v>
       </c>
       <c r="E90">
-        <v>0.08550185873605948</v>
+        <v>0.07556935817805382</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Ciências Exatas e da Terra</t>
+          <t>Engenharias</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Instituto de Física de São Carlos</t>
+          <t>Escola de Engenharia de Lorena</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Bacharelado em Física Computacional</t>
+          <t>Engenharia Ambiental</t>
         </is>
       </c>
       <c r="D91">
-        <v>542</v>
+        <v>278</v>
       </c>
       <c r="E91">
-        <v>0.08487084870848709</v>
+        <v>0.07553956834532374</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Engenharias</t>
+          <t>Ciências Exatas e da Terra</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Escola de Engenharia de Lorena</t>
+          <t>Instituto de Ciências Matemáticas e de Computação</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Engenharia de Produção</t>
+          <t>Bacharelado em Matemática Aplicada e Computação Científica</t>
         </is>
       </c>
       <c r="D92">
-        <v>430</v>
+        <v>252</v>
       </c>
       <c r="E92">
-        <v>0.08372093023255814</v>
+        <v>0.07539682539682539</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Multidisciplinar</t>
+          <t>Ciências Exatas e da Terra</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Faculdade de Filosofia, Ciências e Letras de Ribeirão Preto</t>
+          <t>Instituto de Física de São Carlos</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Música</t>
+          <t>Bacharelado em Física Computacional</t>
         </is>
       </c>
       <c r="D93">
-        <v>343</v>
+        <v>367</v>
       </c>
       <c r="E93">
-        <v>0.08163265306122448</v>
+        <v>0.07084468664850137</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Engenharias</t>
+          <t>Ciências Agrárias</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Escola de Engenharia de Lorena</t>
+          <t>Escola Superior de Agricultura "Luiz de Queiroz"</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Engenharia Ambiental</t>
+          <t>Ciências Econômicas</t>
         </is>
       </c>
       <c r="D94">
-        <v>419</v>
+        <v>386</v>
       </c>
       <c r="E94">
-        <v>0.07875894988066826</v>
+        <v>0.06735751295336788</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Multidisciplinar</t>
+          <t>Linguística, Letras e Artes</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Escola de Artes, Ciências e Humanidades</t>
+          <t>Escola de Comunicações e Artes</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Gerontologia</t>
+          <t>Biblioteconomia</t>
         </is>
       </c>
       <c r="D95">
-        <v>735</v>
+        <v>376</v>
       </c>
       <c r="E95">
-        <v>0.07755102040816327</v>
+        <v>0.06648936170212766</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Ciências Sociais Aplicadas</t>
+          <t>Multidisciplinar</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Faculdade de Economia, Administração e Contabilidade de Ribeirão Preto</t>
+          <t>Escola de Artes, Ciências e Humanidades</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Ciências Contábeis</t>
+          <t>Bacharelado em Gestão Ambiental</t>
         </is>
       </c>
       <c r="D96">
-        <v>614</v>
+        <v>1147</v>
       </c>
       <c r="E96">
-        <v>0.07654723127035831</v>
+        <v>0.06364428945074106</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Ciências Agrárias</t>
+          <t>Multidisciplinar</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Escola Superior de Agricultura "Luiz de Queiroz"</t>
+          <t>Escola de Artes, Ciências e Humanidades</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Gestão Ambiental</t>
+          <t>Bacharelado em Educação Física e Saúde</t>
         </is>
       </c>
       <c r="D97">
-        <v>530</v>
+        <v>541</v>
       </c>
       <c r="E97">
-        <v>0.07547169811320754</v>
+        <v>0.06099815157116451</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Ciências Sociais Aplicadas</t>
+          <t>Linguística, Letras e Artes</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Faculdade de Economia, Administração e Contabilidade de Ribeirão Preto</t>
+          <t>Escola de Comunicações e Artes</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Bacharelado em Administração</t>
+          <t>Licenciatura em Educomunicação</t>
         </is>
       </c>
       <c r="D98">
-        <v>1397</v>
+        <v>281</v>
       </c>
       <c r="E98">
-        <v>0.06800286327845383</v>
+        <v>0.06049822064056939</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Linguística, Letras e Artes</t>
+          <t>Ciências Sociais Aplicadas</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Escola de Comunicações e Artes</t>
+          <t>Faculdade de Economia, Administração, Contabilidade e Atuária</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Bacharelado em Jornalismo</t>
+          <t>Bacharelado em Ciências Econômicas</t>
         </is>
       </c>
       <c r="D99">
-        <v>369</v>
+        <v>1821</v>
       </c>
       <c r="E99">
-        <v>0.06775067750677506</v>
+        <v>0.05985722130697419</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Ciências Humanas</t>
+          <t>Multidisciplinar</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Faculdade de Educação</t>
+          <t>Escola de Artes, Ciências e Humanidades</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Pedagogia</t>
+          <t>Bacharelado em Têxtil e Moda</t>
         </is>
       </c>
       <c r="D100">
-        <v>2623</v>
+        <v>571</v>
       </c>
       <c r="E100">
-        <v>0.0670987418985894</v>
+        <v>0.0595446584938704</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Engenharias</t>
+          <t>Multidisciplinar</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Escola de Engenharia de São Carlos</t>
+          <t>Faculdade de Filosofia, Ciências e Letras de Ribeirão Preto</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Engenharia de Produção</t>
+          <t>Pedagogia</t>
         </is>
       </c>
       <c r="D101">
-        <v>453</v>
+        <v>476</v>
       </c>
       <c r="E101">
-        <v>0.0640176600441501</v>
+        <v>0.05882352941176471</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Linguística, Letras e Artes</t>
+          <t>Ciências Exatas e da Terra</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Escola de Comunicações e Artes</t>
+          <t>Instituto de Matemática e Estatística</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Licenciatura em Educomunicação</t>
+          <t>Bacharelado em Ciência da Computação</t>
         </is>
       </c>
       <c r="D102">
-        <v>424</v>
+        <v>543</v>
       </c>
       <c r="E102">
-        <v>0.06367924528301887</v>
+        <v>0.0570902394106814</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Multidisciplinar</t>
+          <t>Ciências Sociais Aplicadas</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Escola de Artes, Ciências e Humanidades</t>
+          <t>Faculdade de Economia, Administração, Contabilidade e Atuária</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Bacharelado em Gestão Ambiental</t>
+          <t>Bacharelado em Administração</t>
         </is>
       </c>
       <c r="D103">
-        <v>1626</v>
+        <v>2058</v>
       </c>
       <c r="E103">
-        <v>0.06273062730627306</v>
+        <v>0.05636540330417882</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Ciências Exatas e da Terra</t>
+          <t>Engenharias</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Instituto de Matemática e Estatística</t>
+          <t>Escola de Engenharia de Lorena</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Matemática Bacharelado</t>
+          <t>Engenharia de Produção</t>
         </is>
       </c>
       <c r="D104">
-        <v>503</v>
+        <v>269</v>
       </c>
       <c r="E104">
-        <v>0.06163021868787277</v>
+        <v>0.05576208178438662</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Multidisciplinar</t>
+          <t>Ciências Exatas e da Terra</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Faculdade de Filosofia, Ciências e Letras de Ribeirão Preto</t>
+          <t>Instituto de Matemática e Estatística</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Bacharelado em Biblioteconomia e Ciência da Informação</t>
+          <t>Matemática Bacharelado</t>
         </is>
       </c>
       <c r="D105">
-        <v>538</v>
+        <v>355</v>
       </c>
       <c r="E105">
-        <v>0.05947955390334572</v>
+        <v>0.05352112676056338</v>
       </c>
     </row>
     <row r="106">
@@ -2786,221 +2786,221 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Bacharelado em Têxtil e Moda</t>
+          <t>Licenciatura em Ciências da Natureza</t>
         </is>
       </c>
       <c r="D106">
-        <v>826</v>
+        <v>886</v>
       </c>
       <c r="E106">
-        <v>0.05932203389830509</v>
+        <v>0.05304740406320542</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Ciências Exatas e da Terra</t>
+          <t>Multidisciplinar</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Instituto de Matemática e Estatística</t>
+          <t>Faculdade de Filosofia, Ciências e Letras de Ribeirão Preto</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Bacharelado em Ciência da Computação</t>
+          <t>Bacharelado em Matemática Aplicada a Negócios</t>
         </is>
       </c>
       <c r="D107">
-        <v>800</v>
+        <v>290</v>
       </c>
       <c r="E107">
-        <v>0.05875</v>
+        <v>0.05172413793103448</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Ciências Sociais Aplicadas</t>
+          <t>Linguística, Letras e Artes</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Faculdade de Economia, Administração, Contabilidade e Atuária</t>
+          <t>Escola de Comunicações e Artes</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Bacharelado em Ciências Econômicas</t>
+          <t>Bacharelado em Comunicação Social</t>
         </is>
       </c>
       <c r="D108">
-        <v>2581</v>
+        <v>1475</v>
       </c>
       <c r="E108">
-        <v>0.05462998837659822</v>
+        <v>0.05084745762711865</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Linguística, Letras e Artes</t>
+          <t>Multidisciplinar</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Escola de Comunicações e Artes</t>
+          <t>Escola de Artes, Ciências e Humanidades</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Biblioteconomia</t>
+          <t>Bacharelado em Sistemas de Informação</t>
         </is>
       </c>
       <c r="D109">
-        <v>576</v>
+        <v>1636</v>
       </c>
       <c r="E109">
-        <v>0.05381944444444445</v>
+        <v>0.0488997555012225</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Multidisciplinar</t>
+          <t>Ciências Exatas e da Terra</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Faculdade de Filosofia, Ciências e Letras de Ribeirão Preto</t>
+          <t>Instituto de Matemática e Estatística</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Pedagogia</t>
+          <t>Estatística Bacharelado</t>
         </is>
       </c>
       <c r="D110">
-        <v>707</v>
+        <v>443</v>
       </c>
       <c r="E110">
-        <v>0.05374823196605375</v>
+        <v>0.04740406320541761</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Ciências Agrárias</t>
+          <t>Ciências Sociais Aplicadas</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Escola Superior de Agricultura "Luiz de Queiroz"</t>
+          <t>Faculdade de Direito</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Ciências Econômicas</t>
+          <t>Direito</t>
         </is>
       </c>
       <c r="D111">
-        <v>555</v>
+        <v>4251</v>
       </c>
       <c r="E111">
-        <v>0.05225225225225225</v>
+        <v>0.04587155963302753</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Ciências Sociais Aplicadas</t>
+          <t>Linguística, Letras e Artes</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Faculdade de Economia, Administração, Contabilidade e Atuária</t>
+          <t>Escola de Comunicações e Artes</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Bacharelado em Administração</t>
+          <t>Turismo</t>
         </is>
       </c>
       <c r="D112">
-        <v>2947</v>
+        <v>295</v>
       </c>
       <c r="E112">
-        <v>0.05089921954530031</v>
+        <v>0.04406779661016949</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Linguística, Letras e Artes</t>
+          <t>Ciências Exatas e da Terra</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Escola de Comunicações e Artes</t>
+          <t>Instituto de Matemática e Estatística</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Bacharelado em Relações Públicas</t>
+          <t>Matemática Aplicada - Bacharelado</t>
         </is>
       </c>
       <c r="D113">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="E113">
-        <v>0.05</v>
+        <v>0.044</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Multidisciplinar</t>
+          <t>Ciências Exatas e da Terra</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Escola de Artes, Ciências e Humanidades</t>
+          <t>Instituto de Ciências Matemáticas e de Computação</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Bacharelado em Educação Física e Saúde</t>
+          <t>Bacharelado em Estatística</t>
         </is>
       </c>
       <c r="D114">
-        <v>798</v>
+        <v>415</v>
       </c>
       <c r="E114">
-        <v>0.04887218045112782</v>
+        <v>0.04337349397590361</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Linguística, Letras e Artes</t>
+          <t>Ciências Agrárias</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Escola de Comunicações e Artes</t>
+          <t>Escola Superior de Agricultura "Luiz de Queiroz"</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Bacharelado em Comunicação Social</t>
+          <t>Bacharelado em Administração</t>
         </is>
       </c>
       <c r="D115">
-        <v>1744</v>
+        <v>247</v>
       </c>
       <c r="E115">
-        <v>0.04873853211009174</v>
+        <v>0.04048582995951417</v>
       </c>
     </row>
     <row r="116">
@@ -3016,37 +3016,37 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Bacharelado em Estatística</t>
+          <t>Bacharelado em Sistemas de Informação</t>
         </is>
       </c>
       <c r="D116">
-        <v>469</v>
+        <v>450</v>
       </c>
       <c r="E116">
-        <v>0.04690831556503199</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Multidisciplinar</t>
+          <t>Ciências Sociais Aplicadas</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Escola de Artes, Ciências e Humanidades</t>
+          <t>Faculdade de Economia, Administração, Contabilidade e Atuária</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Bacharelado em Sistemas de Informação</t>
+          <t>Bacharelado em Ciências Contábeis</t>
         </is>
       </c>
       <c r="D117">
-        <v>2354</v>
+        <v>1479</v>
       </c>
       <c r="E117">
-        <v>0.04672897196261682</v>
+        <v>0.03989181879648411</v>
       </c>
     </row>
     <row r="118">
@@ -3062,37 +3062,37 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Licenciatura em Ciências da Natureza</t>
+          <t>Gestão de Políticas Públicas</t>
         </is>
       </c>
       <c r="D118">
-        <v>1092</v>
+        <v>1232</v>
       </c>
       <c r="E118">
-        <v>0.0467032967032967</v>
+        <v>0.03733766233766234</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Ciências Exatas e da Terra</t>
+          <t>Ciências Sociais Aplicadas</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Instituto de Matemática e Estatística</t>
+          <t>Faculdade de Economia, Administração, Contabilidade e Atuária</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Estatística Bacharelado</t>
+          <t>Bacharelado em Ciências Atuariais</t>
         </is>
       </c>
       <c r="D119">
-        <v>623</v>
+        <v>491</v>
       </c>
       <c r="E119">
-        <v>0.04654895666131621</v>
+        <v>0.03462321792260693</v>
       </c>
     </row>
     <row r="120">
@@ -3103,111 +3103,111 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Faculdade de Filosofia, Ciências e Letras de Ribeirão Preto</t>
+          <t>Escola de Artes, Ciências e Humanidades</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Bacharelado em Matemática Aplicada a Negócios</t>
+          <t>Bacharelado em Lazer e Turismo</t>
         </is>
       </c>
       <c r="D120">
-        <v>487</v>
+        <v>1129</v>
       </c>
       <c r="E120">
-        <v>0.04517453798767967</v>
+        <v>0.03365810451727192</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Multidisciplinar</t>
+          <t>Ciências Exatas e da Terra</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Escola de Artes, Ciências e Humanidades</t>
+          <t>Instituto de Física</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Gestão de Políticas Públicas</t>
+          <t>Física Licenciatura</t>
         </is>
       </c>
       <c r="D121">
-        <v>1751</v>
+        <v>1187</v>
       </c>
       <c r="E121">
-        <v>0.04169046259280411</v>
+        <v>0.03201347935973041</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Ciências Sociais Aplicadas</t>
+          <t>Multidisciplinar</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Faculdade de Direito</t>
+          <t>Interunidades de Licenciatura IFSC/IQSC/ICMC</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Direito</t>
+          <t>Licenciatura em Ciências Exatas</t>
         </is>
       </c>
       <c r="D122">
-        <v>6180</v>
+        <v>414</v>
       </c>
       <c r="E122">
-        <v>0.04142394822006473</v>
+        <v>0.02898550724637681</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Linguística, Letras e Artes</t>
+          <t>Ciências Exatas e da Terra</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Escola de Comunicações e Artes</t>
+          <t>Instituto de Geociências</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Música Bacharelado</t>
+          <t>Licenciatura em Geociências e Educação Ambiental</t>
         </is>
       </c>
       <c r="D123">
-        <v>220</v>
+        <v>434</v>
       </c>
       <c r="E123">
-        <v>0.04090909090909091</v>
+        <v>0.02764976958525346</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Ciências Exatas e da Terra</t>
+          <t>Multidisciplinar</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Instituto de Matemática e Estatística</t>
+          <t>Escola de Artes, Ciências e Humanidades</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Matemática Aplicada - Bacharelado</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D124">
-        <v>357</v>
+        <v>1130</v>
       </c>
       <c r="E124">
-        <v>0.0392156862745098</v>
+        <v>0.02654867256637168</v>
       </c>
     </row>
     <row r="125">
@@ -3218,294 +3218,64 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Instituto de Física</t>
+          <t>Instituto de Matemática e Estatística</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Física Licenciatura</t>
+          <t>Bacharelado em Matemática Aplicada e Computacional</t>
         </is>
       </c>
       <c r="D125">
-        <v>1706</v>
+        <v>623</v>
       </c>
       <c r="E125">
-        <v>0.03868698710433763</v>
+        <v>0.02086677367576244</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Linguística, Letras e Artes</t>
+          <t>Ciências Exatas e da Terra</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Escola de Comunicações e Artes</t>
+          <t>Instituto de Matemática e Estatística</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Turismo</t>
+          <t>Matemática Licenciatura</t>
         </is>
       </c>
       <c r="D126">
-        <v>427</v>
+        <v>1483</v>
       </c>
       <c r="E126">
-        <v>0.03747072599531616</v>
+        <v>0.009440323668240054</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Ciências Sociais Aplicadas</t>
+          <t>Multidisciplinar</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Faculdade de Economia, Administração, Contabilidade e Atuária</t>
+          <t>Pró-reitoria de Graduação</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Bacharelado em Ciências Contábeis</t>
+          <t>Licenciatura em Ciências</t>
         </is>
       </c>
       <c r="D127">
-        <v>2115</v>
+        <v>1064</v>
       </c>
       <c r="E127">
-        <v>0.03735224586288416</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Ciências Sociais Aplicadas</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Faculdade de Economia, Administração, Contabilidade e Atuária</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Bacharelado em Ciências Atuariais</t>
-        </is>
-      </c>
-      <c r="D128">
-        <v>698</v>
-      </c>
-      <c r="E128">
-        <v>0.0329512893982808</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Ciências Exatas e da Terra</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Instituto de Ciências Matemáticas e de Computação</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Bacharelado em Sistemas de Informação</t>
-        </is>
-      </c>
-      <c r="D129">
-        <v>673</v>
-      </c>
-      <c r="E129">
-        <v>0.03268945022288262</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Ciências Agrárias</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Escola Superior de Agricultura "Luiz de Queiroz"</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Bacharelado em Administração</t>
-        </is>
-      </c>
-      <c r="D130">
-        <v>421</v>
-      </c>
-      <c r="E130">
-        <v>0.03087885985748218</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Multidisciplinar</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Interunidades de Licenciatura IFSC/IQSC/ICMC</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Licenciatura em Ciências Exatas</t>
-        </is>
-      </c>
-      <c r="D131">
-        <v>588</v>
-      </c>
-      <c r="E131">
-        <v>0.0272108843537415</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Multidisciplinar</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Escola de Artes, Ciências e Humanidades</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Bacharelado em Lazer e Turismo</t>
-        </is>
-      </c>
-      <c r="D132">
-        <v>1586</v>
-      </c>
-      <c r="E132">
-        <v>0.02522068095838588</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Multidisciplinar</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Escola de Artes, Ciências e Humanidades</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Marketing</t>
-        </is>
-      </c>
-      <c r="D133">
-        <v>1610</v>
-      </c>
-      <c r="E133">
-        <v>0.02360248447204969</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Ciências Exatas e da Terra</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Instituto de Matemática e Estatística</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Bacharelado em Matemática Aplicada e Computacional</t>
-        </is>
-      </c>
-      <c r="D134">
-        <v>878</v>
-      </c>
-      <c r="E134">
-        <v>0.0193621867881549</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Ciências Exatas e da Terra</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Instituto de Geociências</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Licenciatura em Geociências e Educação Ambiental</t>
-        </is>
-      </c>
-      <c r="D135">
-        <v>625</v>
-      </c>
-      <c r="E135">
-        <v>0.0192</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Ciências Exatas e da Terra</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Instituto de Matemática e Estatística</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Matemática Licenciatura</t>
-        </is>
-      </c>
-      <c r="D136">
-        <v>2138</v>
-      </c>
-      <c r="E136">
-        <v>0.009354536950420954</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Multidisciplinar</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Pró-reitoria de Graduação</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Licenciatura em Ciências</t>
-        </is>
-      </c>
-      <c r="D137">
-        <v>1064</v>
-      </c>
-      <c r="E137">
         <v>0.007518796992481203</v>
       </c>
     </row>
